--- a/src/assets/data/Grupos_66.xlsx
+++ b/src/assets/data/Grupos_66.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jreinoso\IdeaProjects\agenda-jfd-68-cue\src\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E0B457-95EA-4AD9-97BE-5D6084BCF12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0826716D-0228-4156-A167-696D0B911406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{543A5BD2-3525-45AA-91AC-6F75075045CD}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7265" uniqueCount="1895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7319" uniqueCount="1917">
   <si>
     <t>GERAUD EDMOND</t>
   </si>
@@ -5731,6 +5731,72 @@
   </si>
   <si>
     <t>rmacero@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>Taller de Análisis Estadístico e Inteligencia Artificial Aplicados a la Publicación Científica de Alto Impacto - Auditorio Luna Tobar</t>
+  </si>
+  <si>
+    <t>Taller de Diseño y Formulación de Proyectos de Investigación Científica - Auditorio Leonidas Proaño</t>
+  </si>
+  <si>
+    <t>AVILA CARRASCO JESSICA MARIBEL</t>
+  </si>
+  <si>
+    <t>javilac@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>SANTACRUZ ARIAS MARIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>msantacruz@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>ABAD BARRIONUEVO MARIA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>CARDENAS OCHOA JORGE VICTOR</t>
+  </si>
+  <si>
+    <t>ORTIZ GUILLEN YADY CRISTINA</t>
+  </si>
+  <si>
+    <t>PALACIOS VERDUGO MONICA MARCELA</t>
+  </si>
+  <si>
+    <t>PEREZ CASTRO MARIA MERCEDES</t>
+  </si>
+  <si>
+    <t>PINOS LUZURIAGA MARIA KARINA</t>
+  </si>
+  <si>
+    <t>TUZA ROA IRINA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>mabadb@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>jcardenaso@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>1803428596</t>
+  </si>
+  <si>
+    <t>mpalaciosv@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>mperezc1@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>mpinos@ups.edu.ec</t>
+  </si>
+  <si>
+    <t>0104988464</t>
+  </si>
+  <si>
+    <t>0105916290</t>
+  </si>
+  <si>
+    <t>0105242598</t>
   </si>
 </sst>
 </file>
@@ -5740,7 +5806,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000000000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5800,6 +5866,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="23">
@@ -6144,9 +6216,6 @@
     <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6164,7 +6233,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6176,12 +6245,24 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6511,14 +6592,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69FE7164-7D56-4F99-A3FB-492E909C83DA}">
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F431"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.5703125" customWidth="1"/>
     <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="116" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6538,7 +6619,7 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="4" t="s">
         <v>1842</v>
       </c>
     </row>
@@ -6556,7 +6637,7 @@
         <v>1843</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>4</v>
@@ -6636,7 +6717,7 @@
         <v>1844</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1888</v>
@@ -6676,7 +6757,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>4</v>
@@ -6716,7 +6797,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>1891</v>
@@ -6733,10 +6814,10 @@
         <v>1460</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1843</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>1889</v>
@@ -6756,7 +6837,7 @@
         <v>1844</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>4</v>
@@ -6876,7 +6957,7 @@
         <v>1843</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>4</v>
@@ -6916,7 +6997,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>1889</v>
@@ -6936,7 +7017,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>4</v>
@@ -6956,7 +7037,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>4</v>
@@ -6996,7 +7077,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>1890</v>
@@ -7056,7 +7137,7 @@
         <v>1844</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>4</v>
@@ -7096,7 +7177,7 @@
         <v>1844</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>4</v>
@@ -7156,7 +7237,7 @@
         <v>1844</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>4</v>
@@ -7176,7 +7257,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>4</v>
@@ -7236,7 +7317,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>1891</v>
@@ -7256,7 +7337,7 @@
         <v>1843</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>4</v>
@@ -7436,7 +7517,7 @@
         <v>4</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>1888</v>
@@ -7476,7 +7557,7 @@
         <v>4</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>4</v>
@@ -7516,7 +7597,7 @@
         <v>4</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>1891</v>
@@ -7616,7 +7697,7 @@
         <v>4</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>1889</v>
@@ -7636,7 +7717,7 @@
         <v>4</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>1888</v>
@@ -7756,7 +7837,7 @@
         <v>1843</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>1891</v>
@@ -7956,7 +8037,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>1890</v>
@@ -7996,7 +8077,7 @@
         <v>1844</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>1888</v>
@@ -8036,7 +8117,7 @@
         <v>1844</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>4</v>
@@ -8096,7 +8177,7 @@
         <v>4</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>1888</v>
@@ -8176,7 +8257,7 @@
         <v>1844</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>4</v>
@@ -8256,7 +8337,7 @@
         <v>4</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>4</v>
@@ -8296,7 +8377,7 @@
         <v>1844</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>4</v>
@@ -8336,7 +8417,7 @@
         <v>4</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>4</v>
@@ -8396,7 +8477,7 @@
         <v>4</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>1888</v>
@@ -8496,7 +8577,7 @@
         <v>1844</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>1890</v>
@@ -8836,7 +8917,7 @@
         <v>4</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>1890</v>
@@ -8996,7 +9077,7 @@
         <v>4</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>1889</v>
@@ -9016,7 +9097,7 @@
         <v>1844</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>4</v>
@@ -9036,7 +9117,7 @@
         <v>1844</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>4</v>
@@ -9056,7 +9137,7 @@
         <v>1844</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>1890</v>
@@ -9096,7 +9177,7 @@
         <v>4</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>1889</v>
@@ -9116,7 +9197,7 @@
         <v>1843</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>1890</v>
@@ -9136,7 +9217,7 @@
         <v>4</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>4</v>
@@ -9296,7 +9377,7 @@
         <v>4</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>4</v>
@@ -9316,7 +9397,7 @@
         <v>4</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>4</v>
@@ -9336,7 +9417,7 @@
         <v>4</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>1889</v>
@@ -9356,7 +9437,7 @@
         <v>1843</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>4</v>
@@ -9376,7 +9457,7 @@
         <v>1843</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>4</v>
@@ -9396,7 +9477,7 @@
         <v>4</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>1888</v>
@@ -9496,7 +9577,7 @@
         <v>4</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>1891</v>
@@ -10356,7 +10437,7 @@
         <v>4</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>1888</v>
@@ -10496,7 +10577,7 @@
         <v>4</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>4</v>
@@ -10576,7 +10657,7 @@
         <v>1844</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>4</v>
@@ -10656,7 +10737,7 @@
         <v>1843</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>4</v>
@@ -10676,7 +10757,7 @@
         <v>4</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>4</v>
@@ -11016,7 +11097,7 @@
         <v>1843</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>4</v>
@@ -11373,7 +11454,7 @@
         <v>1682</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>4</v>
+        <v>1843</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>4</v>
@@ -11436,7 +11517,7 @@
         <v>4</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>4</v>
@@ -11476,7 +11557,7 @@
         <v>1844</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>4</v>
@@ -11496,7 +11577,7 @@
         <v>1844</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>4</v>
@@ -11876,7 +11957,7 @@
         <v>4</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>1891</v>
@@ -12036,7 +12117,7 @@
         <v>1844</v>
       </c>
       <c r="E276" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>4</v>
@@ -12096,7 +12177,7 @@
         <v>1844</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>4</v>
@@ -12116,7 +12197,7 @@
         <v>1844</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>4</v>
@@ -12296,7 +12377,7 @@
         <v>4</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F289" s="4" t="s">
         <v>1890</v>
@@ -12336,7 +12417,7 @@
         <v>4</v>
       </c>
       <c r="E291" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F291" s="4" t="s">
         <v>1888</v>
@@ -12516,7 +12597,7 @@
         <v>4</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>4</v>
@@ -12536,7 +12617,7 @@
         <v>4</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>1888</v>
@@ -12976,7 +13057,7 @@
         <v>1844</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>4</v>
@@ -13036,7 +13117,7 @@
         <v>4</v>
       </c>
       <c r="E326" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>4</v>
@@ -13116,7 +13197,7 @@
         <v>4</v>
       </c>
       <c r="E330" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>4</v>
@@ -13176,7 +13257,7 @@
         <v>1844</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>4</v>
@@ -13196,7 +13277,7 @@
         <v>4</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>1888</v>
@@ -13356,7 +13437,7 @@
         <v>1843</v>
       </c>
       <c r="E342" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>1891</v>
@@ -13536,7 +13617,7 @@
         <v>4</v>
       </c>
       <c r="E351" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>4</v>
@@ -13636,7 +13717,7 @@
         <v>1844</v>
       </c>
       <c r="E356" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>1888</v>
@@ -13756,7 +13837,7 @@
         <v>1844</v>
       </c>
       <c r="E362" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>4</v>
@@ -13776,7 +13857,7 @@
         <v>1843</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>1888</v>
@@ -13796,7 +13877,7 @@
         <v>4</v>
       </c>
       <c r="E364" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>4</v>
@@ -13856,7 +13937,7 @@
         <v>1843</v>
       </c>
       <c r="E367" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>4</v>
@@ -13976,7 +14057,7 @@
         <v>1843</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>4</v>
+        <v>1896</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>1888</v>
@@ -14036,7 +14117,7 @@
         <v>1844</v>
       </c>
       <c r="E376" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F376" s="4" t="s">
         <v>4</v>
@@ -14496,7 +14577,7 @@
         <v>4</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>4</v>
+        <v>1895</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>4</v>
@@ -14803,13 +14884,13 @@
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A415" s="47" t="s">
+      <c r="A415" s="46" t="s">
         <v>1882</v>
       </c>
-      <c r="B415" s="43" t="s">
+      <c r="B415" s="42" t="s">
         <v>1845</v>
       </c>
-      <c r="C415" s="45" t="s">
+      <c r="C415" s="44" t="s">
         <v>1846</v>
       </c>
       <c r="D415" s="4" t="s">
@@ -14823,13 +14904,13 @@
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A416" s="47" t="s">
+      <c r="A416" s="46" t="s">
         <v>1883</v>
       </c>
-      <c r="B416" s="44" t="s">
+      <c r="B416" s="43" t="s">
         <v>1847</v>
       </c>
-      <c r="C416" s="46" t="s">
+      <c r="C416" s="45" t="s">
         <v>1848</v>
       </c>
       <c r="D416" s="4" t="s">
@@ -14843,13 +14924,13 @@
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A417" s="47" t="s">
+      <c r="A417" s="46" t="s">
         <v>1884</v>
       </c>
-      <c r="B417" s="44" t="s">
+      <c r="B417" s="43" t="s">
         <v>1849</v>
       </c>
-      <c r="C417" s="46" t="s">
+      <c r="C417" s="45" t="s">
         <v>1850</v>
       </c>
       <c r="D417" s="4" t="s">
@@ -14863,13 +14944,13 @@
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A418" s="47" t="s">
+      <c r="A418" s="46" t="s">
         <v>1885</v>
       </c>
-      <c r="B418" s="44" t="s">
+      <c r="B418" s="43" t="s">
         <v>1851</v>
       </c>
-      <c r="C418" s="46" t="s">
+      <c r="C418" s="45" t="s">
         <v>1852</v>
       </c>
       <c r="D418" s="4" t="s">
@@ -14883,13 +14964,13 @@
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A419" s="47" t="s">
+      <c r="A419" s="46" t="s">
         <v>1886</v>
       </c>
-      <c r="B419" s="44" t="s">
+      <c r="B419" s="43" t="s">
         <v>1853</v>
       </c>
-      <c r="C419" s="46" t="s">
+      <c r="C419" s="45" t="s">
         <v>1854</v>
       </c>
       <c r="D419" s="4" t="s">
@@ -14903,33 +14984,33 @@
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A420" s="48" t="s">
+      <c r="A420" s="47" t="s">
         <v>1887</v>
       </c>
-      <c r="B420" s="49" t="s">
+      <c r="B420" s="48" t="s">
         <v>1855</v>
       </c>
-      <c r="C420" s="50" t="s">
+      <c r="C420" s="49" t="s">
         <v>1856</v>
       </c>
-      <c r="D420" s="51" t="s">
+      <c r="D420" s="50" t="s">
         <v>1844</v>
       </c>
-      <c r="E420" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="F420" s="51" t="s">
+      <c r="E420" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F420" s="50" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A421" s="47" t="s">
+      <c r="A421" s="46" t="s">
         <v>1881</v>
       </c>
-      <c r="B421" s="52" t="s">
+      <c r="B421" s="51" t="s">
         <v>1857</v>
       </c>
-      <c r="C421" s="52" t="s">
+      <c r="C421" s="51" t="s">
         <v>1858</v>
       </c>
       <c r="D421" s="4" t="s">
@@ -14943,13 +15024,13 @@
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A422" s="47" t="s">
+      <c r="A422" s="46" t="s">
         <v>1893</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>1892</v>
       </c>
-      <c r="C422" s="53" t="s">
+      <c r="C422" s="52" t="s">
         <v>1894</v>
       </c>
       <c r="D422" s="4" t="s">
@@ -14960,6 +15041,186 @@
       </c>
       <c r="F422" s="4" t="s">
         <v>1890</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A423" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="B423" s="53" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C423" s="53" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A424" s="46" t="s">
+        <v>378</v>
+      </c>
+      <c r="B424" s="51" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C424" s="53" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A425" s="46" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B425" s="51" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F425" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A426" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B426" s="51" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C426" s="28" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E426" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A427" s="46" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B427" s="51" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A428" s="46" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B428" s="51" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C428" s="3" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E428" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A429" s="46" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B429" s="51" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C429" s="28" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E429" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F429" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A430" s="46" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B430" s="51" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E430" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A431" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="B431" s="51" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C431" s="28" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14969,6 +15230,7 @@
     <hyperlink ref="C422" r:id="rId1" xr:uid="{971D44ED-A137-4458-A9A2-887DCAD3CDF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
